--- a/output/pdf_financials_xlsx/RME.xlsx
+++ b/output/pdf_financials_xlsx/RME.xlsx
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.195138</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.2111</v>
       </c>
     </row>
     <row r="93">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.035398</v>
+        <v>-0.001219</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.035398</v>
+        <v>-0.001524</v>
       </c>
     </row>
     <row r="119">
@@ -2638,7 +2638,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>4.195138</v>
       </c>
@@ -2936,7 +2940,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.036617</v>
       </c>

--- a/output/pdf_financials_xlsx/RME.xlsx
+++ b/output/pdf_financials_xlsx/RME.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.445232</v>
+        <v>0.59619</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.531864</v>
+        <v>2.700672</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.445232</v>
+        <v>-0.59619</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.531864</v>
+        <v>-2.700672</v>
       </c>
     </row>
     <row r="12">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.472038</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.021179</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.474038</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.023179</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.472038</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.021179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">

--- a/output/pdf_financials_xlsx/RME.xlsx
+++ b/output/pdf_financials_xlsx/RME.xlsx
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.88493</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.5216</v>
       </c>
     </row>
     <row r="65">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.018464</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="68">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.029271</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.064764</v>
       </c>
     </row>
     <row r="102">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.462775</v>
+        <v>0.433504</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.012597</v>
+        <v>0.947833</v>
       </c>
     </row>
     <row r="107">
@@ -2836,7 +2836,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.005473</v>
       </c>
@@ -2860,7 +2864,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>-0.034744</v>
       </c>
@@ -3076,7 +3084,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.9</v>
       </c>
